--- a/Calculations/water_flow_table.xlsx
+++ b/Calculations/water_flow_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,30 +436,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Qavg (m³/hr)</t>
+          <t>Q averege flow (m³/hr)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Q new peak (m³/hr)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Flow distribution Q (m³/hr)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Difference (Flow-Qavg) (m³/hr)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Amount to Storage (m³)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Amount from Storage (m³)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Running Total in Storage (m³)</t>
         </is>
@@ -475,18 +480,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C2" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D2" t="n">
         <v>2523.2685</v>
       </c>
-      <c r="D2" t="n">
-        <v>-1682.179</v>
-      </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-3133.661500000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1682.179</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>3133.661500000001</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -500,18 +508,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C3" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D3" t="n">
         <v>2102.72375</v>
       </c>
-      <c r="D3" t="n">
-        <v>-2102.72375</v>
-      </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-3554.206250000001</v>
       </c>
       <c r="F3" t="n">
-        <v>2102.72375</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>3554.206250000001</v>
+      </c>
+      <c r="H3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -525,18 +536,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C4" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D4" t="n">
         <v>1682.179</v>
       </c>
-      <c r="D4" t="n">
-        <v>-2523.268499999999</v>
-      </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-3974.751</v>
       </c>
       <c r="F4" t="n">
-        <v>2523.268499999999</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>3974.751</v>
+      </c>
+      <c r="H4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -550,18 +564,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C5" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D5" t="n">
         <v>1261.63425</v>
       </c>
-      <c r="D5" t="n">
-        <v>-2943.813249999999</v>
-      </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-4395.29575</v>
       </c>
       <c r="F5" t="n">
-        <v>2943.813249999999</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>4395.29575</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -575,18 +592,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C6" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D6" t="n">
         <v>1261.63425</v>
       </c>
-      <c r="D6" t="n">
-        <v>-2943.813249999999</v>
-      </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-4395.29575</v>
       </c>
       <c r="F6" t="n">
-        <v>2943.813249999999</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
+        <v>4395.29575</v>
+      </c>
+      <c r="H6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -600,18 +620,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C7" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D7" t="n">
         <v>1682.179</v>
       </c>
-      <c r="D7" t="n">
-        <v>-2523.268499999999</v>
-      </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-3974.751</v>
       </c>
       <c r="F7" t="n">
-        <v>2523.268499999999</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
+        <v>3974.751</v>
+      </c>
+      <c r="H7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -625,18 +648,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C8" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D8" t="n">
         <v>2523.2685</v>
       </c>
-      <c r="D8" t="n">
-        <v>-1682.179</v>
-      </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-3133.661500000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1682.179</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
+        <v>3133.661500000001</v>
+      </c>
+      <c r="H8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -650,18 +676,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C9" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D9" t="n">
         <v>2943.813249999999</v>
       </c>
-      <c r="D9" t="n">
-        <v>-1261.63425</v>
-      </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-2713.116750000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1261.63425</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
+        <v>2713.116750000001</v>
+      </c>
+      <c r="H9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -675,18 +704,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C10" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D10" t="n">
         <v>3364.358</v>
       </c>
-      <c r="D10" t="n">
-        <v>-841.0894999999991</v>
-      </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-2292.572</v>
       </c>
       <c r="F10" t="n">
-        <v>841.0894999999991</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
+        <v>2292.572</v>
+      </c>
+      <c r="H10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -700,18 +732,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C11" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D11" t="n">
         <v>3784.90275</v>
       </c>
-      <c r="D11" t="n">
-        <v>-420.5447499999996</v>
-      </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-1872.027250000001</v>
       </c>
       <c r="F11" t="n">
-        <v>420.5447499999996</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>1872.027250000001</v>
+      </c>
+      <c r="H11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -725,18 +760,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C12" t="n">
-        <v>4205.447499999999</v>
+        <v>5656.93</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>4205.447499999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-1451.482500000001</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
+        <v>1451.482500000001</v>
+      </c>
+      <c r="H12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -750,18 +788,21 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C13" t="n">
-        <v>4205.447499999999</v>
+        <v>5656.93</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4205.447499999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-1451.482500000001</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
+        <v>1451.482500000001</v>
+      </c>
+      <c r="H13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -775,19 +816,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C14" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D14" t="n">
         <v>4625.99225</v>
       </c>
-      <c r="D14" t="n">
-        <v>420.5447500000009</v>
-      </c>
       <c r="E14" t="n">
-        <v>420.5447500000009</v>
+        <v>-1030.93775</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420.5447500000009</v>
+        <v>1030.93775</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -800,19 +844,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C15" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D15" t="n">
         <v>5046.536999999999</v>
       </c>
-      <c r="D15" t="n">
-        <v>841.0895</v>
-      </c>
       <c r="E15" t="n">
-        <v>841.0895</v>
+        <v>-610.3930000000009</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1261.634250000001</v>
+        <v>610.3930000000009</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -825,19 +872,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C16" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D16" t="n">
         <v>5467.08175</v>
       </c>
-      <c r="D16" t="n">
-        <v>1261.634250000001</v>
-      </c>
       <c r="E16" t="n">
-        <v>1261.634250000001</v>
+        <v>-189.84825</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2523.268500000002</v>
+        <v>189.84825</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -850,19 +900,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C17" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D17" t="n">
         <v>5887.626499999998</v>
       </c>
-      <c r="D17" t="n">
-        <v>1682.178999999999</v>
-      </c>
       <c r="E17" t="n">
-        <v>1682.178999999999</v>
+        <v>230.6964999999982</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>230.6964999999982</v>
       </c>
       <c r="G17" t="n">
-        <v>4205.447500000001</v>
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>230.6964999999982</v>
       </c>
     </row>
     <row r="18">
@@ -875,19 +928,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C18" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D18" t="n">
         <v>6728.716</v>
       </c>
-      <c r="D18" t="n">
-        <v>2523.268500000001</v>
-      </c>
       <c r="E18" t="n">
-        <v>2523.268500000001</v>
+        <v>1071.786</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1071.786</v>
       </c>
       <c r="G18" t="n">
-        <v>6728.716000000002</v>
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1302.482499999998</v>
       </c>
     </row>
     <row r="19">
@@ -900,19 +956,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C19" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D19" t="n">
         <v>7149.260749999999</v>
       </c>
-      <c r="D19" t="n">
-        <v>2943.813249999999</v>
-      </c>
       <c r="E19" t="n">
-        <v>2943.813249999999</v>
+        <v>1492.330749999998</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1492.330749999998</v>
       </c>
       <c r="G19" t="n">
-        <v>9672.529250000001</v>
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2794.813249999997</v>
       </c>
     </row>
     <row r="20">
@@ -925,19 +984,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C20" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D20" t="n">
         <v>7990.350249999999</v>
       </c>
-      <c r="D20" t="n">
-        <v>3784.902749999999</v>
-      </c>
       <c r="E20" t="n">
-        <v>3784.902749999999</v>
+        <v>2333.420249999998</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2333.420249999998</v>
       </c>
       <c r="G20" t="n">
-        <v>13457.432</v>
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5128.233499999995</v>
       </c>
     </row>
     <row r="21">
@@ -950,19 +1012,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C21" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D21" t="n">
         <v>7569.805499999999</v>
       </c>
-      <c r="D21" t="n">
-        <v>3364.358</v>
-      </c>
       <c r="E21" t="n">
-        <v>3364.358</v>
+        <v>1912.875499999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1912.875499999999</v>
       </c>
       <c r="G21" t="n">
-        <v>16821.79</v>
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7041.108999999994</v>
       </c>
     </row>
     <row r="22">
@@ -975,19 +1040,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C22" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D22" t="n">
         <v>6728.716</v>
       </c>
-      <c r="D22" t="n">
-        <v>2523.268500000001</v>
-      </c>
       <c r="E22" t="n">
-        <v>2523.268500000001</v>
+        <v>1071.786</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1071.786</v>
       </c>
       <c r="G22" t="n">
-        <v>19345.0585</v>
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8112.894999999994</v>
       </c>
     </row>
     <row r="23">
@@ -1000,19 +1068,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C23" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D23" t="n">
         <v>5046.536999999999</v>
       </c>
-      <c r="D23" t="n">
-        <v>841.0895</v>
-      </c>
       <c r="E23" t="n">
-        <v>841.0895</v>
+        <v>-610.3930000000009</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>20186.148</v>
+        <v>610.3930000000009</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7502.501999999993</v>
       </c>
     </row>
     <row r="24">
@@ -1025,19 +1096,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C24" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D24" t="n">
         <v>3784.90275</v>
       </c>
-      <c r="D24" t="n">
-        <v>-420.5447499999996</v>
-      </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-1872.027250000001</v>
       </c>
       <c r="F24" t="n">
-        <v>420.5447499999996</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>19765.60325</v>
+        <v>1872.027250000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5630.474749999992</v>
       </c>
     </row>
     <row r="25">
@@ -1050,19 +1124,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C25" t="n">
+        <v>5656.93</v>
+      </c>
+      <c r="D25" t="n">
         <v>2943.813249999999</v>
       </c>
-      <c r="D25" t="n">
-        <v>-1261.63425</v>
-      </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-2713.116750000001</v>
       </c>
       <c r="F25" t="n">
-        <v>1261.63425</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>18503.969</v>
+        <v>2713.116750000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2917.357999999991</v>
       </c>
     </row>
   </sheetData>

--- a/Calculations/water_flow_table.xlsx
+++ b/Calculations/water_flow_table.xlsx
@@ -480,19 +480,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C2" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D2" t="n">
         <v>2523.2685</v>
       </c>
       <c r="E2" t="n">
-        <v>-3133.661500000001</v>
+        <v>-3252.824833333334</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3133.661500000001</v>
+        <v>3252.824833333334</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -508,19 +508,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C3" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D3" t="n">
         <v>2102.72375</v>
       </c>
       <c r="E3" t="n">
-        <v>-3554.206250000001</v>
+        <v>-3673.369583333334</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3554.206250000001</v>
+        <v>3673.369583333334</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -536,19 +536,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C4" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D4" t="n">
         <v>1682.179</v>
       </c>
       <c r="E4" t="n">
-        <v>-3974.751</v>
+        <v>-4093.914333333333</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3974.751</v>
+        <v>4093.914333333333</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -564,19 +564,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C5" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D5" t="n">
         <v>1261.63425</v>
       </c>
       <c r="E5" t="n">
-        <v>-4395.29575</v>
+        <v>-4514.459083333333</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4395.29575</v>
+        <v>4514.459083333333</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -592,19 +592,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C6" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D6" t="n">
         <v>1261.63425</v>
       </c>
       <c r="E6" t="n">
-        <v>-4395.29575</v>
+        <v>-4514.459083333333</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4395.29575</v>
+        <v>4514.459083333333</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -620,19 +620,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C7" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D7" t="n">
         <v>1682.179</v>
       </c>
       <c r="E7" t="n">
-        <v>-3974.751</v>
+        <v>-4093.914333333333</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3974.751</v>
+        <v>4093.914333333333</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -648,19 +648,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C8" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D8" t="n">
         <v>2523.2685</v>
       </c>
       <c r="E8" t="n">
-        <v>-3133.661500000001</v>
+        <v>-3252.824833333334</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3133.661500000001</v>
+        <v>3252.824833333334</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -676,19 +676,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C9" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D9" t="n">
         <v>2943.813249999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-2713.116750000001</v>
+        <v>-2832.280083333334</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2713.116750000001</v>
+        <v>2832.280083333334</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -704,19 +704,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C10" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D10" t="n">
         <v>3364.358</v>
       </c>
       <c r="E10" t="n">
-        <v>-2292.572</v>
+        <v>-2411.735333333333</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2292.572</v>
+        <v>2411.735333333333</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -732,19 +732,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C11" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D11" t="n">
         <v>3784.90275</v>
       </c>
       <c r="E11" t="n">
-        <v>-1872.027250000001</v>
+        <v>-1991.190583333334</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1872.027250000001</v>
+        <v>1991.190583333334</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -760,19 +760,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C12" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D12" t="n">
         <v>4205.447499999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-1451.482500000001</v>
+        <v>-1570.645833333334</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1451.482500000001</v>
+        <v>1570.645833333334</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -788,19 +788,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C13" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D13" t="n">
         <v>4205.447499999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1451.482500000001</v>
+        <v>-1570.645833333334</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1451.482500000001</v>
+        <v>1570.645833333334</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -816,19 +816,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C14" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D14" t="n">
         <v>4625.99225</v>
       </c>
       <c r="E14" t="n">
-        <v>-1030.93775</v>
+        <v>-1150.101083333333</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1030.93775</v>
+        <v>1150.101083333333</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -844,19 +844,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C15" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D15" t="n">
         <v>5046.536999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-610.3930000000009</v>
+        <v>-729.5563333333339</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>610.3930000000009</v>
+        <v>729.5563333333339</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -872,19 +872,19 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C16" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D16" t="n">
         <v>5467.08175</v>
       </c>
       <c r="E16" t="n">
-        <v>-189.84825</v>
+        <v>-309.011583333333</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>189.84825</v>
+        <v>309.011583333333</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -900,22 +900,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C17" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D17" t="n">
         <v>5887.626499999998</v>
       </c>
       <c r="E17" t="n">
-        <v>230.6964999999982</v>
+        <v>111.5331666666652</v>
       </c>
       <c r="F17" t="n">
-        <v>230.6964999999982</v>
+        <v>111.5331666666652</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>230.6964999999982</v>
+        <v>111.5331666666652</v>
       </c>
     </row>
     <row r="18">
@@ -928,22 +928,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C18" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D18" t="n">
         <v>6728.716</v>
       </c>
       <c r="E18" t="n">
-        <v>1071.786</v>
+        <v>952.6226666666671</v>
       </c>
       <c r="F18" t="n">
-        <v>1071.786</v>
+        <v>952.6226666666671</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1302.482499999998</v>
+        <v>1064.155833333332</v>
       </c>
     </row>
     <row r="19">
@@ -956,22 +956,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C19" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D19" t="n">
         <v>7149.260749999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1492.330749999998</v>
+        <v>1373.167416666665</v>
       </c>
       <c r="F19" t="n">
-        <v>1492.330749999998</v>
+        <v>1373.167416666665</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2794.813249999997</v>
+        <v>2437.323249999998</v>
       </c>
     </row>
     <row r="20">
@@ -984,22 +984,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C20" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D20" t="n">
         <v>7990.350249999999</v>
       </c>
       <c r="E20" t="n">
-        <v>2333.420249999998</v>
+        <v>2214.256916666665</v>
       </c>
       <c r="F20" t="n">
-        <v>2333.420249999998</v>
+        <v>2214.256916666665</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5128.233499999995</v>
+        <v>4651.580166666663</v>
       </c>
     </row>
     <row r="21">
@@ -1012,22 +1012,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C21" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D21" t="n">
         <v>7569.805499999999</v>
       </c>
       <c r="E21" t="n">
-        <v>1912.875499999999</v>
+        <v>1793.712166666666</v>
       </c>
       <c r="F21" t="n">
-        <v>1912.875499999999</v>
+        <v>1793.712166666666</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>7041.108999999994</v>
+        <v>6445.292333333329</v>
       </c>
     </row>
     <row r="22">
@@ -1040,22 +1040,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C22" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D22" t="n">
         <v>6728.716</v>
       </c>
       <c r="E22" t="n">
-        <v>1071.786</v>
+        <v>952.6226666666671</v>
       </c>
       <c r="F22" t="n">
-        <v>1071.786</v>
+        <v>952.6226666666671</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>8112.894999999994</v>
+        <v>7397.914999999996</v>
       </c>
     </row>
     <row r="23">
@@ -1068,22 +1068,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C23" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D23" t="n">
         <v>5046.536999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-610.3930000000009</v>
+        <v>-729.5563333333339</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>610.3930000000009</v>
+        <v>729.5563333333339</v>
       </c>
       <c r="H23" t="n">
-        <v>7502.501999999993</v>
+        <v>6668.358666666662</v>
       </c>
     </row>
     <row r="24">
@@ -1096,22 +1096,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C24" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D24" t="n">
         <v>3784.90275</v>
       </c>
       <c r="E24" t="n">
-        <v>-1872.027250000001</v>
+        <v>-1991.190583333334</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1872.027250000001</v>
+        <v>1991.190583333334</v>
       </c>
       <c r="H24" t="n">
-        <v>5630.474749999992</v>
+        <v>4677.168083333328</v>
       </c>
     </row>
     <row r="25">
@@ -1124,22 +1124,22 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C25" t="n">
-        <v>5656.93</v>
+        <v>5776.093333333333</v>
       </c>
       <c r="D25" t="n">
         <v>2943.813249999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-2713.116750000001</v>
+        <v>-2832.280083333334</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2713.116750000001</v>
+        <v>2832.280083333334</v>
       </c>
       <c r="H25" t="n">
-        <v>2917.357999999991</v>
+        <v>1844.887999999994</v>
       </c>
     </row>
   </sheetData>

--- a/Calculations/water_flow_table.xlsx
+++ b/Calculations/water_flow_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Q averege flow (m³/hr)</t>
+          <t>Q average flow (m³/hr)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -451,20 +451,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Difference (Flow-Q new peak) (m³/hr)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Difference (Flow-Qavg) (m³/hr)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Amount to Storage (m³)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Amount from Storage (m³)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Running Total in Storage (m³)</t>
         </is>
@@ -489,12 +494,15 @@
         <v>-3252.824833333334</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-1682.179</v>
       </c>
       <c r="G2" t="n">
-        <v>3252.824833333334</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -517,12 +525,15 @@
         <v>-3673.369583333334</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-2102.72375</v>
       </c>
       <c r="G3" t="n">
-        <v>3673.369583333334</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -545,12 +556,15 @@
         <v>-4093.914333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-2523.268499999999</v>
       </c>
       <c r="G4" t="n">
-        <v>4093.914333333333</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -573,12 +587,15 @@
         <v>-4514.459083333333</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-2943.813249999999</v>
       </c>
       <c r="G5" t="n">
-        <v>4514.459083333333</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -601,12 +618,15 @@
         <v>-4514.459083333333</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-2943.813249999999</v>
       </c>
       <c r="G6" t="n">
-        <v>4514.459083333333</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -629,12 +649,15 @@
         <v>-4093.914333333333</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-2523.268499999999</v>
       </c>
       <c r="G7" t="n">
-        <v>4093.914333333333</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -657,12 +680,15 @@
         <v>-3252.824833333334</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-1682.179</v>
       </c>
       <c r="G8" t="n">
-        <v>3252.824833333334</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -685,12 +711,15 @@
         <v>-2832.280083333334</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-1261.63425</v>
       </c>
       <c r="G9" t="n">
-        <v>2832.280083333334</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -713,12 +742,15 @@
         <v>-2411.735333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-841.0894999999991</v>
       </c>
       <c r="G10" t="n">
-        <v>2411.735333333333</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -741,12 +773,15 @@
         <v>-1991.190583333334</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-420.5447499999996</v>
       </c>
       <c r="G11" t="n">
-        <v>1991.190583333334</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -772,9 +807,12 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1570.645833333334</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -800,9 +838,12 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1570.645833333334</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -825,12 +866,15 @@
         <v>-1150.101083333333</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>420.5447500000009</v>
       </c>
       <c r="G14" t="n">
-        <v>1150.101083333333</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -853,12 +897,15 @@
         <v>-729.5563333333339</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>841.0895</v>
       </c>
       <c r="G15" t="n">
-        <v>729.5563333333339</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -881,12 +928,15 @@
         <v>-309.011583333333</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1261.634250000001</v>
       </c>
       <c r="G16" t="n">
-        <v>309.011583333333</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -909,12 +959,15 @@
         <v>111.5331666666652</v>
       </c>
       <c r="F17" t="n">
+        <v>1682.178999999999</v>
+      </c>
+      <c r="G17" t="n">
         <v>111.5331666666652</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>111.5331666666652</v>
       </c>
     </row>
@@ -937,12 +990,15 @@
         <v>952.6226666666671</v>
       </c>
       <c r="F18" t="n">
+        <v>2523.268500000001</v>
+      </c>
+      <c r="G18" t="n">
         <v>952.6226666666671</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>1064.155833333332</v>
       </c>
     </row>
@@ -965,12 +1021,15 @@
         <v>1373.167416666665</v>
       </c>
       <c r="F19" t="n">
+        <v>2943.813249999999</v>
+      </c>
+      <c r="G19" t="n">
         <v>1373.167416666665</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>2437.323249999998</v>
       </c>
     </row>
@@ -993,12 +1052,15 @@
         <v>2214.256916666665</v>
       </c>
       <c r="F20" t="n">
+        <v>3784.902749999999</v>
+      </c>
+      <c r="G20" t="n">
         <v>2214.256916666665</v>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>4651.580166666663</v>
       </c>
     </row>
@@ -1021,12 +1083,15 @@
         <v>1793.712166666666</v>
       </c>
       <c r="F21" t="n">
+        <v>3364.358</v>
+      </c>
+      <c r="G21" t="n">
         <v>1793.712166666666</v>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>6445.292333333329</v>
       </c>
     </row>
@@ -1049,12 +1114,15 @@
         <v>952.6226666666671</v>
       </c>
       <c r="F22" t="n">
+        <v>2523.268500000001</v>
+      </c>
+      <c r="G22" t="n">
         <v>952.6226666666671</v>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>7397.914999999996</v>
       </c>
     </row>
@@ -1077,13 +1145,16 @@
         <v>-729.5563333333339</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>841.0895</v>
       </c>
       <c r="G23" t="n">
-        <v>729.5563333333339</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>6668.358666666662</v>
+        <v>841.0895</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6556.825499999996</v>
       </c>
     </row>
     <row r="24">
@@ -1105,13 +1176,16 @@
         <v>-1991.190583333334</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-420.5447499999996</v>
       </c>
       <c r="G24" t="n">
-        <v>1991.190583333334</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4677.168083333328</v>
+        <v>420.5447499999996</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6136.280749999996</v>
       </c>
     </row>
     <row r="25">
@@ -1133,13 +1207,16 @@
         <v>-2832.280083333334</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-1261.63425</v>
       </c>
       <c r="G25" t="n">
-        <v>2832.280083333334</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1844.887999999994</v>
+        <v>1261.63425</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4874.646499999996</v>
       </c>
     </row>
   </sheetData>

--- a/Calculations/water_flow_table.xlsx
+++ b/Calculations/water_flow_table.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Q average flow (m³/hr)</t>
+          <t>Q average projected flow (m³/hr)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -446,17 +446,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Flow distribution Q (m³/hr)</t>
+          <t>Flow distribution projected Q (m³/hr)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Difference (Flow-Q new peak) (m³/hr)</t>
+          <t>Difference (Flow projected-Q new peak) (m³/hr)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Difference (Flow-Qavg) (m³/hr)</t>
+          <t>Difference (Flow projected-Qavg) (m³/hr)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -485,13 +485,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C2" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D2" t="n">
         <v>2523.2685</v>
       </c>
       <c r="E2" t="n">
-        <v>-3252.824833333334</v>
+        <v>-2102.281500000001</v>
       </c>
       <c r="F2" t="n">
         <v>-1682.179</v>
@@ -516,13 +516,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C3" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D3" t="n">
         <v>2102.72375</v>
       </c>
       <c r="E3" t="n">
-        <v>-3673.369583333334</v>
+        <v>-2522.826250000001</v>
       </c>
       <c r="F3" t="n">
         <v>-2102.72375</v>
@@ -547,13 +547,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C4" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D4" t="n">
         <v>1682.179</v>
       </c>
       <c r="E4" t="n">
-        <v>-4093.914333333333</v>
+        <v>-2943.371</v>
       </c>
       <c r="F4" t="n">
         <v>-2523.268499999999</v>
@@ -578,13 +578,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C5" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D5" t="n">
         <v>1261.63425</v>
       </c>
       <c r="E5" t="n">
-        <v>-4514.459083333333</v>
+        <v>-3363.91575</v>
       </c>
       <c r="F5" t="n">
         <v>-2943.813249999999</v>
@@ -609,13 +609,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C6" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D6" t="n">
         <v>1261.63425</v>
       </c>
       <c r="E6" t="n">
-        <v>-4514.459083333333</v>
+        <v>-3363.91575</v>
       </c>
       <c r="F6" t="n">
         <v>-2943.813249999999</v>
@@ -640,13 +640,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C7" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D7" t="n">
         <v>1682.179</v>
       </c>
       <c r="E7" t="n">
-        <v>-4093.914333333333</v>
+        <v>-2943.371</v>
       </c>
       <c r="F7" t="n">
         <v>-2523.268499999999</v>
@@ -671,13 +671,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C8" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D8" t="n">
         <v>2523.2685</v>
       </c>
       <c r="E8" t="n">
-        <v>-3252.824833333334</v>
+        <v>-2102.281500000001</v>
       </c>
       <c r="F8" t="n">
         <v>-1682.179</v>
@@ -702,13 +702,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C9" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D9" t="n">
         <v>2943.813249999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-2832.280083333334</v>
+        <v>-1681.736750000001</v>
       </c>
       <c r="F9" t="n">
         <v>-1261.63425</v>
@@ -733,13 +733,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C10" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D10" t="n">
         <v>3364.358</v>
       </c>
       <c r="E10" t="n">
-        <v>-2411.735333333333</v>
+        <v>-1261.192</v>
       </c>
       <c r="F10" t="n">
         <v>-841.0894999999991</v>
@@ -764,13 +764,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C11" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D11" t="n">
         <v>3784.90275</v>
       </c>
       <c r="E11" t="n">
-        <v>-1991.190583333334</v>
+        <v>-840.6472500000004</v>
       </c>
       <c r="F11" t="n">
         <v>-420.5447499999996</v>
@@ -795,13 +795,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C12" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D12" t="n">
         <v>4205.447499999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-1570.645833333334</v>
+        <v>-420.1025000000009</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -826,13 +826,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C13" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D13" t="n">
         <v>4205.447499999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1570.645833333334</v>
+        <v>-420.1025000000009</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -857,25 +857,25 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C14" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D14" t="n">
         <v>4625.99225</v>
       </c>
       <c r="E14" t="n">
-        <v>-1150.101083333333</v>
+        <v>0.4422500000000582</v>
       </c>
       <c r="F14" t="n">
         <v>420.5447500000009</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.4422500000000582</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.4422500000000582</v>
       </c>
     </row>
     <row r="15">
@@ -888,25 +888,25 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C15" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D15" t="n">
         <v>5046.536999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-729.5563333333339</v>
+        <v>420.9869999999992</v>
       </c>
       <c r="F15" t="n">
         <v>841.0895</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>420.9869999999992</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>421.4292499999992</v>
       </c>
     </row>
     <row r="16">
@@ -919,25 +919,25 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C16" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D16" t="n">
         <v>5467.08175</v>
       </c>
       <c r="E16" t="n">
-        <v>-309.011583333333</v>
+        <v>841.5317500000001</v>
       </c>
       <c r="F16" t="n">
         <v>1261.634250000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>841.5317500000001</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1262.960999999999</v>
       </c>
     </row>
     <row r="17">
@@ -950,25 +950,25 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C17" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D17" t="n">
         <v>5887.626499999998</v>
       </c>
       <c r="E17" t="n">
-        <v>111.5331666666652</v>
+        <v>1262.076499999998</v>
       </c>
       <c r="F17" t="n">
         <v>1682.178999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>111.5331666666652</v>
+        <v>1262.076499999998</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>111.5331666666652</v>
+        <v>2525.037499999998</v>
       </c>
     </row>
     <row r="18">
@@ -981,25 +981,25 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C18" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D18" t="n">
         <v>6728.716</v>
       </c>
       <c r="E18" t="n">
-        <v>952.6226666666671</v>
+        <v>2103.166</v>
       </c>
       <c r="F18" t="n">
         <v>2523.268500000001</v>
       </c>
       <c r="G18" t="n">
-        <v>952.6226666666671</v>
+        <v>2103.166</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1064.155833333332</v>
+        <v>4628.203499999998</v>
       </c>
     </row>
     <row r="19">
@@ -1012,25 +1012,25 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C19" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D19" t="n">
         <v>7149.260749999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1373.167416666665</v>
+        <v>2523.710749999998</v>
       </c>
       <c r="F19" t="n">
         <v>2943.813249999999</v>
       </c>
       <c r="G19" t="n">
-        <v>1373.167416666665</v>
+        <v>2523.710749999998</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2437.323249999998</v>
+        <v>7151.914249999996</v>
       </c>
     </row>
     <row r="20">
@@ -1043,25 +1043,25 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C20" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D20" t="n">
         <v>7990.350249999999</v>
       </c>
       <c r="E20" t="n">
-        <v>2214.256916666665</v>
+        <v>3364.800249999998</v>
       </c>
       <c r="F20" t="n">
         <v>3784.902749999999</v>
       </c>
       <c r="G20" t="n">
-        <v>2214.256916666665</v>
+        <v>3364.800249999998</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4651.580166666663</v>
+        <v>10516.71449999999</v>
       </c>
     </row>
     <row r="21">
@@ -1074,25 +1074,25 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C21" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D21" t="n">
         <v>7569.805499999999</v>
       </c>
       <c r="E21" t="n">
-        <v>1793.712166666666</v>
+        <v>2944.255499999999</v>
       </c>
       <c r="F21" t="n">
         <v>3364.358</v>
       </c>
       <c r="G21" t="n">
-        <v>1793.712166666666</v>
+        <v>2944.255499999999</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>6445.292333333329</v>
+        <v>13460.96999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1105,25 +1105,25 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C22" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D22" t="n">
         <v>6728.716</v>
       </c>
       <c r="E22" t="n">
-        <v>952.6226666666671</v>
+        <v>2103.166</v>
       </c>
       <c r="F22" t="n">
         <v>2523.268500000001</v>
       </c>
       <c r="G22" t="n">
-        <v>952.6226666666671</v>
+        <v>2103.166</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>7397.914999999996</v>
+        <v>15564.13599999999</v>
       </c>
     </row>
     <row r="23">
@@ -1136,25 +1136,25 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C23" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D23" t="n">
         <v>5046.536999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-729.5563333333339</v>
+        <v>420.9869999999992</v>
       </c>
       <c r="F23" t="n">
         <v>841.0895</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>420.9869999999992</v>
       </c>
       <c r="H23" t="n">
-        <v>841.0895</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>6556.825499999996</v>
+        <v>15985.12299999999</v>
       </c>
     </row>
     <row r="24">
@@ -1167,13 +1167,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C24" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D24" t="n">
         <v>3784.90275</v>
       </c>
       <c r="E24" t="n">
-        <v>-1991.190583333334</v>
+        <v>-840.6472500000004</v>
       </c>
       <c r="F24" t="n">
         <v>-420.5447499999996</v>
@@ -1185,7 +1185,7 @@
         <v>420.5447499999996</v>
       </c>
       <c r="I24" t="n">
-        <v>6136.280749999996</v>
+        <v>15564.57825</v>
       </c>
     </row>
     <row r="25">
@@ -1198,13 +1198,13 @@
         <v>4205.447499999999</v>
       </c>
       <c r="C25" t="n">
-        <v>5776.093333333333</v>
+        <v>4625.55</v>
       </c>
       <c r="D25" t="n">
         <v>2943.813249999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-2832.280083333334</v>
+        <v>-1681.736750000001</v>
       </c>
       <c r="F25" t="n">
         <v>-1261.63425</v>
@@ -1216,7 +1216,7 @@
         <v>1261.63425</v>
       </c>
       <c r="I25" t="n">
-        <v>4874.646499999996</v>
+        <v>14302.944</v>
       </c>
     </row>
   </sheetData>

--- a/Calculations/water_flow_table.xlsx
+++ b/Calculations/water_flow_table.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C2" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D2" t="n">
-        <v>2523.2685</v>
+        <v>2708.09375</v>
       </c>
       <c r="E2" t="n">
-        <v>-2102.281500000001</v>
+        <v>-2060.83625</v>
       </c>
       <c r="F2" t="n">
-        <v>-1682.179</v>
+        <v>-1805.395833333333</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C3" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D3" t="n">
-        <v>2102.72375</v>
+        <v>2256.744791666667</v>
       </c>
       <c r="E3" t="n">
-        <v>-2522.826250000001</v>
+        <v>-2512.185208333334</v>
       </c>
       <c r="F3" t="n">
-        <v>-2102.72375</v>
+        <v>-2256.744791666667</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -544,19 +544,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C4" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D4" t="n">
-        <v>1682.179</v>
+        <v>1805.395833333333</v>
       </c>
       <c r="E4" t="n">
-        <v>-2943.371</v>
+        <v>-2963.534166666667</v>
       </c>
       <c r="F4" t="n">
-        <v>-2523.268499999999</v>
+        <v>-2708.09375</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C5" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D5" t="n">
-        <v>1261.63425</v>
+        <v>1354.046875</v>
       </c>
       <c r="E5" t="n">
-        <v>-3363.91575</v>
+        <v>-3414.883125</v>
       </c>
       <c r="F5" t="n">
-        <v>-2943.813249999999</v>
+        <v>-3159.442708333333</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C6" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D6" t="n">
-        <v>1261.63425</v>
+        <v>1354.046875</v>
       </c>
       <c r="E6" t="n">
-        <v>-3363.91575</v>
+        <v>-3414.883125</v>
       </c>
       <c r="F6" t="n">
-        <v>-2943.813249999999</v>
+        <v>-3159.442708333333</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -637,19 +637,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C7" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D7" t="n">
-        <v>1682.179</v>
+        <v>1805.395833333333</v>
       </c>
       <c r="E7" t="n">
-        <v>-2943.371</v>
+        <v>-2963.534166666667</v>
       </c>
       <c r="F7" t="n">
-        <v>-2523.268499999999</v>
+        <v>-2708.09375</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -668,19 +668,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C8" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D8" t="n">
-        <v>2523.2685</v>
+        <v>2708.09375</v>
       </c>
       <c r="E8" t="n">
-        <v>-2102.281500000001</v>
+        <v>-2060.83625</v>
       </c>
       <c r="F8" t="n">
-        <v>-1682.179</v>
+        <v>-1805.395833333333</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -699,19 +699,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C9" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D9" t="n">
-        <v>2943.813249999999</v>
+        <v>3159.442708333333</v>
       </c>
       <c r="E9" t="n">
-        <v>-1681.736750000001</v>
+        <v>-1609.487291666667</v>
       </c>
       <c r="F9" t="n">
-        <v>-1261.63425</v>
+        <v>-1354.046875</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C10" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D10" t="n">
-        <v>3364.358</v>
+        <v>3610.791666666667</v>
       </c>
       <c r="E10" t="n">
-        <v>-1261.192</v>
+        <v>-1158.138333333334</v>
       </c>
       <c r="F10" t="n">
-        <v>-841.0894999999991</v>
+        <v>-902.6979166666665</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C11" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D11" t="n">
-        <v>3784.90275</v>
+        <v>4062.140625</v>
       </c>
       <c r="E11" t="n">
-        <v>-840.6472500000004</v>
+        <v>-706.7893750000003</v>
       </c>
       <c r="F11" t="n">
-        <v>-420.5447499999996</v>
+        <v>-451.348958333333</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C12" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D12" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="E12" t="n">
-        <v>-420.1025000000009</v>
+        <v>-255.4404166666673</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -823,16 +823,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C13" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D13" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="E13" t="n">
-        <v>-420.1025000000009</v>
+        <v>-255.4404166666673</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -854,28 +854,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C14" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D14" t="n">
-        <v>4625.99225</v>
+        <v>4964.838541666667</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4422500000000582</v>
+        <v>195.9085416666667</v>
       </c>
       <c r="F14" t="n">
-        <v>420.5447500000009</v>
+        <v>451.3489583333339</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4422500000000582</v>
+        <v>195.9085416666667</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4422500000000582</v>
+        <v>195.9085416666667</v>
       </c>
     </row>
     <row r="15">
@@ -885,28 +885,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C15" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D15" t="n">
-        <v>5046.536999999999</v>
+        <v>5416.1875</v>
       </c>
       <c r="E15" t="n">
-        <v>420.9869999999992</v>
+        <v>647.2574999999997</v>
       </c>
       <c r="F15" t="n">
-        <v>841.0895</v>
+        <v>902.697916666667</v>
       </c>
       <c r="G15" t="n">
-        <v>420.9869999999992</v>
+        <v>647.2574999999997</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>421.4292499999992</v>
+        <v>843.1660416666664</v>
       </c>
     </row>
     <row r="16">
@@ -916,28 +916,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C16" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D16" t="n">
-        <v>5467.08175</v>
+        <v>5867.536458333333</v>
       </c>
       <c r="E16" t="n">
-        <v>841.5317500000001</v>
+        <v>1098.606458333333</v>
       </c>
       <c r="F16" t="n">
-        <v>1261.634250000001</v>
+        <v>1354.046875</v>
       </c>
       <c r="G16" t="n">
-        <v>841.5317500000001</v>
+        <v>1098.606458333333</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1262.960999999999</v>
+        <v>1941.772499999999</v>
       </c>
     </row>
     <row r="17">
@@ -947,28 +947,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C17" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D17" t="n">
-        <v>5887.626499999998</v>
+        <v>6318.885416666667</v>
       </c>
       <c r="E17" t="n">
-        <v>1262.076499999998</v>
+        <v>1549.955416666667</v>
       </c>
       <c r="F17" t="n">
-        <v>1682.178999999999</v>
+        <v>1805.395833333334</v>
       </c>
       <c r="G17" t="n">
-        <v>1262.076499999998</v>
+        <v>1549.955416666667</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2525.037499999998</v>
+        <v>3491.727916666666</v>
       </c>
     </row>
     <row r="18">
@@ -978,28 +978,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C18" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D18" t="n">
-        <v>6728.716</v>
+        <v>7221.583333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>2103.166</v>
+        <v>2452.653333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>2523.268500000001</v>
+        <v>2708.09375</v>
       </c>
       <c r="G18" t="n">
-        <v>2103.166</v>
+        <v>2452.653333333333</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4628.203499999998</v>
+        <v>5944.381249999999</v>
       </c>
     </row>
     <row r="19">
@@ -1009,28 +1009,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C19" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D19" t="n">
-        <v>7149.260749999999</v>
+        <v>7672.932291666667</v>
       </c>
       <c r="E19" t="n">
-        <v>2523.710749999998</v>
+        <v>2904.002291666667</v>
       </c>
       <c r="F19" t="n">
-        <v>2943.813249999999</v>
+        <v>3159.442708333334</v>
       </c>
       <c r="G19" t="n">
-        <v>2523.710749999998</v>
+        <v>2904.002291666667</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>7151.914249999996</v>
+        <v>8848.383541666666</v>
       </c>
     </row>
     <row r="20">
@@ -1040,28 +1040,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C20" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D20" t="n">
-        <v>7990.350249999999</v>
+        <v>8575.630208333334</v>
       </c>
       <c r="E20" t="n">
-        <v>3364.800249999998</v>
+        <v>3806.700208333334</v>
       </c>
       <c r="F20" t="n">
-        <v>3784.902749999999</v>
+        <v>4062.140625000001</v>
       </c>
       <c r="G20" t="n">
-        <v>3364.800249999998</v>
+        <v>3806.700208333334</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>10516.71449999999</v>
+        <v>12655.08375</v>
       </c>
     </row>
     <row r="21">
@@ -1071,28 +1071,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C21" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D21" t="n">
-        <v>7569.805499999999</v>
+        <v>8124.28125</v>
       </c>
       <c r="E21" t="n">
-        <v>2944.255499999999</v>
+        <v>3355.35125</v>
       </c>
       <c r="F21" t="n">
-        <v>3364.358</v>
+        <v>3610.791666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>2944.255499999999</v>
+        <v>3355.35125</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>13460.96999999999</v>
+        <v>16010.435</v>
       </c>
     </row>
     <row r="22">
@@ -1102,28 +1102,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C22" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D22" t="n">
-        <v>6728.716</v>
+        <v>7221.583333333333</v>
       </c>
       <c r="E22" t="n">
-        <v>2103.166</v>
+        <v>2452.653333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>2523.268500000001</v>
+        <v>2708.09375</v>
       </c>
       <c r="G22" t="n">
-        <v>2103.166</v>
+        <v>2452.653333333333</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>15564.13599999999</v>
+        <v>18463.08833333333</v>
       </c>
     </row>
     <row r="23">
@@ -1133,28 +1133,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C23" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D23" t="n">
-        <v>5046.536999999999</v>
+        <v>5416.1875</v>
       </c>
       <c r="E23" t="n">
-        <v>420.9869999999992</v>
+        <v>647.2574999999997</v>
       </c>
       <c r="F23" t="n">
-        <v>841.0895</v>
+        <v>902.697916666667</v>
       </c>
       <c r="G23" t="n">
-        <v>420.9869999999992</v>
+        <v>647.2574999999997</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>15985.12299999999</v>
+        <v>19110.34583333333</v>
       </c>
     </row>
     <row r="24">
@@ -1164,28 +1164,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C24" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D24" t="n">
-        <v>3784.90275</v>
+        <v>4062.140625</v>
       </c>
       <c r="E24" t="n">
-        <v>-840.6472500000004</v>
+        <v>-706.7893750000003</v>
       </c>
       <c r="F24" t="n">
-        <v>-420.5447499999996</v>
+        <v>-451.348958333333</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>420.5447499999996</v>
+        <v>451.348958333333</v>
       </c>
       <c r="I24" t="n">
-        <v>15564.57825</v>
+        <v>18658.996875</v>
       </c>
     </row>
     <row r="25">
@@ -1195,28 +1195,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4205.447499999999</v>
+        <v>4513.489583333333</v>
       </c>
       <c r="C25" t="n">
-        <v>4625.55</v>
+        <v>4768.93</v>
       </c>
       <c r="D25" t="n">
-        <v>2943.813249999999</v>
+        <v>3159.442708333333</v>
       </c>
       <c r="E25" t="n">
-        <v>-1681.736750000001</v>
+        <v>-1609.487291666667</v>
       </c>
       <c r="F25" t="n">
-        <v>-1261.63425</v>
+        <v>-1354.046875</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1261.63425</v>
+        <v>1354.046875</v>
       </c>
       <c r="I25" t="n">
-        <v>14302.944</v>
+        <v>17304.95</v>
       </c>
     </row>
   </sheetData>
